--- a/daily/2026-04-01.xlsx
+++ b/daily/2026-04-01.xlsx
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="E5" t="n">
         <v>21.3</v>
@@ -854,10 +854,10 @@
         <v>80</v>
       </c>
       <c r="P5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
         <v>2.1</v>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="n">
         <v>13.3</v>
@@ -1179,13 +1179,13 @@
         <v>7.2</v>
       </c>
       <c r="O9" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P9" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="R9" t="n">
         <v>4.1</v>
@@ -1538,7 +1538,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1548,73 +1548,73 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>6.2</v>
+        <v>11.6</v>
       </c>
       <c r="G14" t="n">
-        <v>8.6</v>
+        <v>18.2</v>
       </c>
       <c r="H14" t="n">
-        <v>7.3</v>
+        <v>21</v>
       </c>
       <c r="I14" t="n">
-        <v>6.7</v>
+        <v>21.4</v>
       </c>
       <c r="J14" t="n">
-        <v>20.6</v>
+        <v>26.3</v>
       </c>
       <c r="K14" t="n">
-        <v>17.7</v>
+        <v>31.9</v>
       </c>
       <c r="L14" t="n">
-        <v>41.6</v>
+        <v>49.7</v>
       </c>
       <c r="M14" t="n">
-        <v>35.1</v>
+        <v>48.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="O14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P14" t="n">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8</v>
+        <v>9.9</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.5</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>-5.6</v>
       </c>
       <c r="U14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V14" t="n">
         <v>6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>9.8 (4g)</t>
+          <t>25.8 (5g)</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>17.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="n">
         <v>12.3</v>
@@ -2474,10 +2474,10 @@
         <v>40</v>
       </c>
       <c r="P25" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9</v>
+        <v>-1.9</v>
       </c>
       <c r="R25" t="n">
         <v>2.2</v>
@@ -3966,7 +3966,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3980,55 +3980,55 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>25.5</v>
+        <v>14.5</v>
       </c>
       <c r="E44" t="n">
-        <v>24</v>
+        <v>18.7</v>
       </c>
       <c r="F44" t="n">
-        <v>28.4</v>
+        <v>15.6</v>
       </c>
       <c r="G44" t="n">
-        <v>26.2</v>
+        <v>17</v>
       </c>
       <c r="H44" t="n">
-        <v>25.4</v>
+        <v>16.6</v>
       </c>
       <c r="I44" t="n">
-        <v>25.2</v>
+        <v>15.9</v>
       </c>
       <c r="J44" t="n">
-        <v>36.3</v>
+        <v>38.2</v>
       </c>
       <c r="K44" t="n">
         <v>35.7</v>
       </c>
       <c r="L44" t="n">
-        <v>54.3</v>
+        <v>42.5</v>
       </c>
       <c r="M44" t="n">
-        <v>53</v>
+        <v>48.3</v>
       </c>
       <c r="N44" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="O44" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P44" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="Q44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R44" t="n">
         <v>-0.3</v>
       </c>
-      <c r="R44" t="n">
-        <v>3.2</v>
-      </c>
       <c r="S44" t="n">
-        <v>1.3</v>
+        <v>-5.8</v>
       </c>
       <c r="T44" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="U44" t="n">
         <v>23</v>
@@ -4036,15 +4036,19 @@
       <c r="V44" t="n">
         <v>14</v>
       </c>
-      <c r="W44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>11.0 (3g)</t>
+        </is>
+      </c>
       <c r="X44" t="n">
-        <v>13.1</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4058,55 +4062,55 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16.5</v>
+        <v>25.5</v>
       </c>
       <c r="E45" t="n">
-        <v>18.7</v>
+        <v>24</v>
       </c>
       <c r="F45" t="n">
-        <v>15.6</v>
+        <v>28.4</v>
       </c>
       <c r="G45" t="n">
-        <v>17</v>
+        <v>26.2</v>
       </c>
       <c r="H45" t="n">
-        <v>16.6</v>
+        <v>25.4</v>
       </c>
       <c r="I45" t="n">
-        <v>15.9</v>
+        <v>25.2</v>
       </c>
       <c r="J45" t="n">
-        <v>38.2</v>
+        <v>36.3</v>
       </c>
       <c r="K45" t="n">
         <v>35.7</v>
       </c>
       <c r="L45" t="n">
-        <v>42.5</v>
+        <v>54.3</v>
       </c>
       <c r="M45" t="n">
-        <v>48.3</v>
+        <v>53</v>
       </c>
       <c r="N45" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="O45" t="n">
         <v>50</v>
       </c>
       <c r="P45" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.3</v>
+        <v>3.2</v>
       </c>
       <c r="S45" t="n">
-        <v>-5.8</v>
+        <v>1.3</v>
       </c>
       <c r="T45" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="U45" t="n">
         <v>23</v>
@@ -4114,13 +4118,9 @@
       <c r="V45" t="n">
         <v>14</v>
       </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>11.0 (3g)</t>
-        </is>
-      </c>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="n">
-        <v>-7.6</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="46">
@@ -4208,7 +4208,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Gary Trent Jr.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4218,79 +4218,79 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
       <c r="E47" t="n">
-        <v>16</v>
+        <v>22.3</v>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>17.4</v>
       </c>
       <c r="G47" t="n">
-        <v>9.1</v>
+        <v>11.9</v>
       </c>
       <c r="H47" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
       <c r="J47" t="n">
-        <v>24.6</v>
+        <v>22.1</v>
       </c>
       <c r="K47" t="n">
-        <v>27.8</v>
+        <v>16.5</v>
       </c>
       <c r="L47" t="n">
-        <v>31.6</v>
+        <v>37.9</v>
       </c>
       <c r="M47" t="n">
-        <v>36.9</v>
+        <v>32.7</v>
       </c>
       <c r="N47" t="n">
-        <v>5.3</v>
+        <v>10.7</v>
       </c>
       <c r="O47" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P47" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.1</v>
+        <v>-8</v>
       </c>
       <c r="R47" t="n">
-        <v>1.4</v>
+        <v>9.9</v>
       </c>
       <c r="S47" t="n">
-        <v>-5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T47" t="n">
-        <v>-3.3</v>
+        <v>5.6</v>
       </c>
       <c r="U47" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="V47" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>9.0 (3g)</t>
+          <t>8.7 (3g)</t>
         </is>
       </c>
       <c r="X47" t="n">
-        <v>-3.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gary Trent Jr.</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4300,73 +4300,73 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.5</v>
+        <v>9.5</v>
       </c>
       <c r="E48" t="n">
-        <v>22.3</v>
+        <v>16</v>
       </c>
       <c r="F48" t="n">
-        <v>17.4</v>
+        <v>11</v>
       </c>
       <c r="G48" t="n">
-        <v>11.9</v>
+        <v>9.1</v>
       </c>
       <c r="H48" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>7.5</v>
+        <v>9.6</v>
       </c>
       <c r="J48" t="n">
-        <v>22.1</v>
+        <v>24.6</v>
       </c>
       <c r="K48" t="n">
-        <v>16.5</v>
+        <v>27.8</v>
       </c>
       <c r="L48" t="n">
-        <v>37.9</v>
+        <v>31.6</v>
       </c>
       <c r="M48" t="n">
-        <v>32.7</v>
+        <v>36.9</v>
       </c>
       <c r="N48" t="n">
-        <v>10.7</v>
+        <v>5.3</v>
       </c>
       <c r="O48" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P48" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="Q48" t="n">
-        <v>-6</v>
+        <v>0.1</v>
       </c>
       <c r="R48" t="n">
-        <v>9.9</v>
+        <v>1.4</v>
       </c>
       <c r="S48" t="n">
-        <v>5.2</v>
+        <v>-5.3</v>
       </c>
       <c r="T48" t="n">
-        <v>5.6</v>
+        <v>-3.3</v>
       </c>
       <c r="U48" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="V48" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>8.7 (3g)</t>
+          <t>9.0 (3g)</t>
         </is>
       </c>
       <c r="X48" t="n">
-        <v>7.9</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="49">
@@ -5418,7 +5418,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5428,79 +5428,75 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>18.5</v>
+        <v>22.5</v>
       </c>
       <c r="E62" t="n">
-        <v>20.7</v>
+        <v>22</v>
       </c>
       <c r="F62" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G62" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="H62" t="n">
-        <v>17.4</v>
+        <v>19.9</v>
       </c>
       <c r="I62" t="n">
-        <v>17.6</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>30.9</v>
+        <v>30.3</v>
       </c>
       <c r="K62" t="n">
-        <v>28.7</v>
+        <v>29.8</v>
       </c>
       <c r="L62" t="n">
-        <v>49.7</v>
+        <v>54.5</v>
       </c>
       <c r="M62" t="n">
-        <v>45.8</v>
+        <v>49</v>
       </c>
       <c r="N62" t="n">
-        <v>13.8</v>
+        <v>5.3</v>
       </c>
       <c r="O62" t="n">
         <v>50</v>
       </c>
       <c r="P62" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.9</v>
+        <v>-3.5</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.6</v>
+        <v>2</v>
       </c>
       <c r="S62" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="T62" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="U62" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="V62" t="n">
-        <v>25</v>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>23.0 (3g)</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="n">
-        <v>-2.2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5510,75 +5506,79 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="E63" t="n">
-        <v>11</v>
+        <v>20.7</v>
       </c>
       <c r="F63" t="n">
-        <v>9.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="G63" t="n">
-        <v>8.800000000000001</v>
+        <v>20.6</v>
       </c>
       <c r="H63" t="n">
-        <v>9.4</v>
+        <v>17.4</v>
       </c>
       <c r="I63" t="n">
-        <v>8.699999999999999</v>
+        <v>17.6</v>
       </c>
       <c r="J63" t="n">
-        <v>21.6</v>
+        <v>30.9</v>
       </c>
       <c r="K63" t="n">
-        <v>25.1</v>
+        <v>28.7</v>
       </c>
       <c r="L63" t="n">
-        <v>71.40000000000001</v>
+        <v>49.7</v>
       </c>
       <c r="M63" t="n">
-        <v>59.8</v>
+        <v>45.8</v>
       </c>
       <c r="N63" t="n">
-        <v>4.6</v>
+        <v>13.8</v>
       </c>
       <c r="O63" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="P63" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="Q63" t="n">
-        <v>-2.8</v>
+        <v>-0.9</v>
       </c>
       <c r="R63" t="n">
-        <v>0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="S63" t="n">
-        <v>11.6</v>
+        <v>3.9</v>
       </c>
       <c r="T63" t="n">
-        <v>-3.5</v>
+        <v>2.2</v>
       </c>
       <c r="U63" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V63" t="n">
-        <v>15</v>
-      </c>
-      <c r="W63" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>23.0 (3g)</t>
+        </is>
+      </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5588,20 +5588,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="E64" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
-        <v>11.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>11.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H64" t="n">
         <v>9.4</v>
@@ -5610,53 +5610,53 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>23.9</v>
+        <v>21.6</v>
       </c>
       <c r="K64" t="n">
-        <v>21.9</v>
+        <v>25.1</v>
       </c>
       <c r="L64" t="n">
-        <v>55.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M64" t="n">
-        <v>41.4</v>
+        <v>59.8</v>
       </c>
       <c r="N64" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="O64" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="P64" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="Q64" t="n">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="R64" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="S64" t="n">
-        <v>13.7</v>
+        <v>11.6</v>
       </c>
       <c r="T64" t="n">
-        <v>2</v>
+        <v>-3.5</v>
       </c>
       <c r="U64" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="V64" t="n">
         <v>15</v>
       </c>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
-        <v>-32.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5666,69 +5666,69 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>21.5</v>
+        <v>10.5</v>
       </c>
       <c r="E65" t="n">
-        <v>22</v>
+        <v>10.7</v>
       </c>
       <c r="F65" t="n">
-        <v>21</v>
+        <v>11.6</v>
       </c>
       <c r="G65" t="n">
-        <v>20.8</v>
+        <v>11.8</v>
       </c>
       <c r="H65" t="n">
-        <v>19.9</v>
+        <v>9.4</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>30.3</v>
+        <v>23.9</v>
       </c>
       <c r="K65" t="n">
-        <v>29.8</v>
+        <v>21.9</v>
       </c>
       <c r="L65" t="n">
-        <v>54.5</v>
+        <v>55.1</v>
       </c>
       <c r="M65" t="n">
-        <v>49</v>
+        <v>41.4</v>
       </c>
       <c r="N65" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="O65" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P65" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Q65" t="n">
-        <v>-2.5</v>
+        <v>-1.8</v>
       </c>
       <c r="R65" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S65" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="T65" t="n">
         <v>2</v>
       </c>
-      <c r="S65" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0.5</v>
-      </c>
       <c r="U65" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="V65" t="n">
         <v>15</v>
       </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="n">
-        <v>-5</v>
+        <v>-32.6</v>
       </c>
     </row>
     <row r="66">
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="E74" t="n">
         <v>14</v>
@@ -6417,13 +6417,13 @@
         <v>7.1</v>
       </c>
       <c r="O74" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P74" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R74" t="n">
         <v>-0.1</v>
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="E81" t="n">
         <v>22.7</v>
@@ -6982,10 +6982,10 @@
         <v>70</v>
       </c>
       <c r="P81" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Q81" t="n">
-        <v>-3.4</v>
+        <v>-4.4</v>
       </c>
       <c r="R81" t="n">
         <v>6.7</v>
@@ -9373,10 +9373,10 @@
         <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.333</v>
+        <v>1.385</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -9421,10 +9421,10 @@
         <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.364</v>
+        <v>1.345</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.635</v>
+        <v>0.667</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -9466,17 +9466,17 @@
         <v>24</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>1.408</v>
+        <v>1.385</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.1 pts (L5 vs L30) — supports the OVER. TS% shifts +6.1% in this matchup; FG% +6.4% trending (L10 vs L30). Opponent is below-average defense (#18) at slow pace (#29). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; H2H, Pace, Min Trend dissent. Projection model targets 24.0 pts (4.5 pts above line; 63% blended confidence [T2]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 2.1 pts (L5 vs L30) — supports the OVER. TS% shifts +6.1% in this matchup; FG% +6.4% trending (L10 vs L30). Opponent is below-average defense (#18) at slow pace (#29). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Pace, Min Trend dissent. Projection model targets 24.0 pts (5.5 pts above line; 66% blended confidence [T2]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -9517,10 +9517,10 @@
         <v>5.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="K6" t="n">
-        <v>1.357</v>
+        <v>1.417</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -9565,10 +9565,10 @@
         <v>5.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>1.345</v>
+        <v>1.435</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -9646,29 +9646,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.54</v>
+        <v>0.552</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4</v>
+        <v>1.435</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 4.1 pts (L5 vs L30) — marginally supports the UNDER. FG% +3.8% trending (L10 vs L30). Opponent is below-average defense (#18) at slow pace (#29). Mixed signals: 2/10 agree (Context, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.0 pts (0.5 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=7.2) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 4.1 pts (L5 vs L30) — marginally supports the UNDER. FG% +3.8% trending (L10 vs L30). Opponent is below-average defense (#18) at slow pace (#29). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 10.9 pts (1.6 pts below line; 55% blended confidence [T3]). Risk: high variance (σ=7.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -9709,10 +9709,10 @@
         <v>0.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K10" t="n">
-        <v>1.408</v>
+        <v>1.385</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -9805,10 +9805,10 @@
         <v>5.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>1.408</v>
+        <v>1.385</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9886,29 +9886,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.556</v>
+        <v>0.726</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>10.7</v>
+        <v>18.8</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="K14" t="n">
-        <v>1.69</v>
+        <v>1.893</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.9) — highly predictable output near line — marginally supports the OVER. H2H avg 3.1 pts above season L30; TS% shifts +17.9% in this matchup. Opponent is below-average defense (#20) at above-average pace (#6). Mixed signals: 5/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 10.7 pts (2.2 pts above line; 55% blended confidence [T3]). Risk: only 37% hit rate over L30 suggests the line may be set fairly.</t>
+          <t>Wagner averages 25.8 pts in 5 meetings (+14.3 vs line) — supports the OVER. H2H avg 4.4 pts above season L30; Minutes down 5.6 recently (L10=26.3 vs L30=31.9). Opponent is weak defense (#24) at above-average pace (#6). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Min Trend dissent. Projection model targets 18.8 pts (7.3 pts above line; 72% blended confidence [T3]). Risk: L3 has dropped to 11.0 (10.4 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
@@ -9949,10 +9949,10 @@
         <v>3.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.943</v>
+        <v>1.901</v>
       </c>
       <c r="K15" t="n">
-        <v>1.82</v>
+        <v>1.862</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -10045,10 +10045,10 @@
         <v>1.9</v>
       </c>
       <c r="J17" t="n">
-        <v>1.877</v>
+        <v>1.87</v>
       </c>
       <c r="K17" t="n">
-        <v>1.877</v>
+        <v>1.893</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -10093,10 +10093,10 @@
         <v>1.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1.909</v>
+        <v>1.926</v>
       </c>
       <c r="K18" t="n">
-        <v>1.847</v>
+        <v>1.833</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -10141,10 +10141,10 @@
         <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1.971</v>
+        <v>1.917</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -10189,10 +10189,10 @@
         <v>3.3</v>
       </c>
       <c r="J20" t="n">
-        <v>1.87</v>
+        <v>1.952</v>
       </c>
       <c r="K20" t="n">
-        <v>1.893</v>
+        <v>1.813</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -10285,10 +10285,10 @@
         <v>3.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1.952</v>
+        <v>1.98</v>
       </c>
       <c r="K22" t="n">
-        <v>1.813</v>
+        <v>1.787</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -10333,10 +10333,10 @@
         <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>1.84</v>
+        <v>1.971</v>
       </c>
       <c r="K23" t="n">
-        <v>1.917</v>
+        <v>1.8</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -10381,10 +10381,10 @@
         <v>0.8</v>
       </c>
       <c r="J24" t="n">
+        <v>1.893</v>
+      </c>
+      <c r="K24" t="n">
         <v>1.87</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.893</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
@@ -10414,10 +10414,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.537</v>
+        <v>0.514</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -10426,17 +10426,17 @@
         <v>12.9</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
-        <v>1.917</v>
+        <v>1.952</v>
       </c>
       <c r="K25" t="n">
-        <v>1.84</v>
+        <v>1.813</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Vukcevic averages 14.8 pts in 4 meetings (+3.3 vs line) — supports the OVER. H2H avg 4.2 pts above season L30; TS% shifts +4.1% in this matchup. Opponent is below-average defense (#21) at slow pace (#23). 6/10 signals agree — Trend, Context, Defense, H2H support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 12.9 pts (1.4 pts above line; 53% blended confidence [T3]).</t>
+          <t>Vukcevic averages 14.8 pts in 4 meetings (+2.3 vs line) — marginally supports the OVER. H2H avg 4.2 pts above season L30; TS% shifts +4.1% in this matchup. Opponent is below-average defense (#21) at slow pace (#23). Mixed signals: 5/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 12.9 pts (0.4 pts above line; 51% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -10477,10 +10477,10 @@
         <v>1.3</v>
       </c>
       <c r="J26" t="n">
-        <v>1.943</v>
+        <v>1.926</v>
       </c>
       <c r="K26" t="n">
-        <v>1.82</v>
+        <v>1.833</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -10621,10 +10621,10 @@
         <v>2.9</v>
       </c>
       <c r="J29" t="n">
-        <v>1.769</v>
+        <v>1.699</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -10669,10 +10669,10 @@
         <v>5.2</v>
       </c>
       <c r="J30" t="n">
-        <v>1.952</v>
+        <v>1.943</v>
       </c>
       <c r="K30" t="n">
-        <v>1.813</v>
+        <v>1.82</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
@@ -10717,10 +10717,10 @@
         <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>1.813</v>
+        <v>1.87</v>
       </c>
       <c r="K31" t="n">
-        <v>1.952</v>
+        <v>1.893</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -10909,10 +10909,10 @@
         <v>0.7</v>
       </c>
       <c r="J35" t="n">
-        <v>1.787</v>
+        <v>1.813</v>
       </c>
       <c r="K35" t="n">
-        <v>1.98</v>
+        <v>1.962</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
@@ -11005,10 +11005,10 @@
         <v>0.3</v>
       </c>
       <c r="J37" t="n">
-        <v>1.82</v>
+        <v>1.813</v>
       </c>
       <c r="K37" t="n">
-        <v>1.943</v>
+        <v>1.952</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -11053,10 +11053,10 @@
         <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>1.952</v>
+        <v>1.943</v>
       </c>
       <c r="K38" t="n">
-        <v>1.813</v>
+        <v>1.82</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
@@ -11101,10 +11101,10 @@
         <v>4.6</v>
       </c>
       <c r="J39" t="n">
-        <v>1.87</v>
+        <v>1.901</v>
       </c>
       <c r="K39" t="n">
-        <v>1.87</v>
+        <v>1.847</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -11149,10 +11149,10 @@
         <v>12.1</v>
       </c>
       <c r="J40" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="K40" t="n">
-        <v>1.345</v>
+        <v>1.4</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -11197,10 +11197,10 @@
         <v>2.3</v>
       </c>
       <c r="J41" t="n">
-        <v>1.87</v>
+        <v>1.901</v>
       </c>
       <c r="K41" t="n">
-        <v>1.87</v>
+        <v>1.833</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
@@ -11245,10 +11245,10 @@
         <v>3.1</v>
       </c>
       <c r="J42" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="K42" t="n">
-        <v>1.943</v>
+        <v>1.476</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -11293,10 +11293,10 @@
         <v>3.1</v>
       </c>
       <c r="J43" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="K43" t="n">
-        <v>1.435</v>
+        <v>1.385</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11317,45 +11317,45 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.571</v>
+        <v>0.593</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>27.9</v>
+        <v>11.5</v>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>1.87</v>
+        <v>1.769</v>
       </c>
       <c r="K44" t="n">
-        <v>1.87</v>
+        <v>1.952</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 3.2 pts (L5 vs L30) — supports the OVER. Opponent is weak defense (#23) at moderate pace (#14). 6/10 signals agree — Trend, Context, Defense, Pace support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 27.9 pts (2.4 pts above line; 57% blended confidence [T2]).</t>
+          <t>Jr. averages 11.0 pts in 3 meetings (-3.5 vs line) — marginally supports the UNDER. H2H avg 4.9 pts below season L30; TS% shifts -7.6% in this matchup. Opponent is weak defense (#23) at moderate pace (#14). Mixed signals: 3/10 agree (Trend, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.5 pts (3.0 pts below line; 59% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.629</v>
+        <v>0.571</v>
       </c>
       <c r="F45" t="n">
         <v>6</v>
@@ -11383,10 +11383,10 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>11.6</v>
+        <v>27.9</v>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>1.769</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Jr. averages 11.0 pts in 3 meetings (-5.5 vs line) — supports the UNDER. H2H avg 4.9 pts below season L30; TS% shifts -7.6% in this matchup. Opponent is weak defense (#23) at moderate pace (#14). 6/10 signals agree — Volume, HR L30, Trend, Context support the UNDER; HR L10, Defense, Pace dissent. Projection model targets 11.6 pts (4.9 pts below line; 62% blended confidence [T2]).</t>
+          <t>Recent scoring trending up 3.2 pts (L5 vs L30) — supports the OVER. Opponent is weak defense (#23) at moderate pace (#14). 6/10 signals agree — Trend, Context, Defense, Pace support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 27.9 pts (2.4 pts above line; 57% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
@@ -11437,10 +11437,10 @@
         <v>3.1</v>
       </c>
       <c r="J46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K46" t="n">
         <v>1.952</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1.8</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Gary Trent Jr.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -11470,36 +11470,36 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.546</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J47" t="n">
-        <v>1.909</v>
+        <v>2.7</v>
       </c>
       <c r="K47" t="n">
-        <v>1.833</v>
+        <v>1.435</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Eason's L30 average of 9.6 pts vs the 9.5 line — marginally supports the UNDER. TS% shifts -3.7% in this matchup; FG% -5.3% trending (L10 vs L30). Opponent is weak defense (#23) at moderate pace (#14). Mixed signals: 5/10 agree (HR L30, Context, H2H); counter-signals: Volume, HR L10, Trend. Projection model targets 7.6 pts (1.9 pts below line; 54% blended confidence [T3]). Risk: L3 has surged to 16.0 after a 11-pt outing (6.4 above L30) — momentum could push over the under line.</t>
+          <t>Jr.'s L30 of 7.5 pts sits 8.0 below the 15.5 line — supports the UNDER. TS% shifts +7.9% in this matchup; FG% +5.2% trending (L10 vs L30). Opponent is elite defense (#5) at slow pace (#22). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, FG Trend, Min Trend dissent. Projection model targets 8.7 pts (6.8 pts below line; 69% blended confidence [T3]). Risk: L3 has surged to 22.3 after a 15-pt outing (14.8 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gary Trent Jr.</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -11518,29 +11518,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.642</v>
+        <v>0.546</v>
       </c>
       <c r="F48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I48" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>1.952</v>
       </c>
       <c r="K48" t="n">
-        <v>1.364</v>
+        <v>1.8</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 9.9 pts (L5 vs L30) — supports the UNDER. TS% shifts +7.9% in this matchup; FG% +5.2% trending (L10 vs L30). Opponent is elite defense (#5) at slow pace (#22). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, FG Trend, Min Trend dissent. Projection model targets 8.7 pts (4.8 pts below line; 64% blended confidence [T3]). Risk: L3 has surged to 22.3 after a 15-pt outing (14.8 above L30) — momentum could push over the under line.</t>
+          <t>Eason's L30 average of 9.6 pts vs the 9.5 line — marginally supports the UNDER. TS% shifts -3.7% in this matchup; FG% -5.3% trending (L10 vs L30). Opponent is weak defense (#23) at moderate pace (#14). Mixed signals: 5/10 agree (HR L30, Context, H2H); counter-signals: Volume, HR L10, Trend. Projection model targets 7.6 pts (1.9 pts below line; 54% blended confidence [T3]). Risk: L3 has surged to 16.0 after a 11-pt outing (6.4 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -11581,10 +11581,10 @@
         <v>1.1</v>
       </c>
       <c r="J49" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="K49" t="n">
-        <v>1.73</v>
+        <v>1.719</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -11725,10 +11725,10 @@
         <v>1.5</v>
       </c>
       <c r="J52" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K52" t="n">
-        <v>1.333</v>
+        <v>1.357</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
@@ -11917,10 +11917,10 @@
         <v>5.4</v>
       </c>
       <c r="J56" t="n">
-        <v>1.877</v>
+        <v>3.05</v>
       </c>
       <c r="K56" t="n">
-        <v>1.877</v>
+        <v>1.357</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
@@ -11965,10 +11965,10 @@
         <v>1.6</v>
       </c>
       <c r="J57" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="K57" t="n">
-        <v>1.476</v>
+        <v>1.385</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
@@ -12013,10 +12013,10 @@
         <v>1.4</v>
       </c>
       <c r="J58" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="K58" t="n">
-        <v>1.408</v>
+        <v>1.357</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
@@ -12061,10 +12061,10 @@
         <v>0.6</v>
       </c>
       <c r="J59" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
-        <v>1.476</v>
+        <v>1.364</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
@@ -12157,10 +12157,10 @@
         <v>2.7</v>
       </c>
       <c r="J61" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>1.435</v>
+        <v>1.364</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -12181,45 +12181,45 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.542</v>
+        <v>0.527</v>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>20.7</v>
+        <v>22.6</v>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="J62" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
-        <v>1.417</v>
+        <v>1.364</v>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>DeRozan averages 23.0 pts in 3 meetings (+4.5 vs line) — marginally supports the OVER. H2H avg 5.4 pts above season L30; FG% +3.9% trending (L10 vs L30). Opponent is average defense (#13) at slow pace (#25). Mixed signals: 4/10 agree (Context, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 20.7 pts (2.2 pts above line; 54% blended confidence [T3]). Risk: high variance (σ=13.8) makes the outcome difficult to call with confidence.</t>
+          <t>[Low conviction — lean only] Barrett's L30 of 19.0 pts sits 3.5 below the 22.5 line — marginally supports the lean UNDER. FG% +5.5% trending (L10 vs L30). Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 22.6 pts (0.1 pts above line; 52% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12238,36 +12238,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.632</v>
+        <v>0.542</v>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>7.5</v>
+        <v>20.7</v>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="K63" t="n">
-        <v>1.408</v>
+        <v>1.417</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Murray-Boyles's L30 of 8.7 pts sits 2.8 below the 11.5 line — marginally supports the UNDER. FG% +11.6% trending (L10 vs L30); Minutes down 3.5 recently (L10=21.6 vs L30=25.1). Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 7.5 pts (4.0 pts below line; 63% blended confidence [T3]). Risk: minutes trending down (21.6 L10 vs 25.1 L30) — role reduction would suppress counting stats.</t>
+          <t>DeRozan averages 23.0 pts in 3 meetings (+4.5 vs line) — marginally supports the OVER. H2H avg 5.4 pts above season L30; FG% +3.9% trending (L10 vs L30). Opponent is average defense (#13) at slow pace (#25). Mixed signals: 4/10 agree (Context, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 20.7 pts (2.2 pts above line; 54% blended confidence [T3]). Risk: high variance (σ=13.8) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12286,36 +12286,36 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.765</v>
+        <v>0.632</v>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.5</v>
+        <v>7.5</v>
       </c>
       <c r="I64" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="K64" t="n">
-        <v>1.435</v>
+        <v>1.455</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.9 pts (L5 vs L30) — marginally supports the UNDER. FG% +13.7% trending (L10 vs L30); Minutes up 2.0 recently (L10=23.9 vs L30=21.9). Opponent is weak defense (#25) at moderate pace (#15). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets -0.5 pts (11.0 pts below line; 76% blended confidence [T3]).</t>
+          <t>Murray-Boyles's L30 of 8.7 pts sits 2.8 below the 11.5 line — marginally supports the UNDER. FG% +11.6% trending (L10 vs L30); Minutes down 3.5 recently (L10=21.6 vs L30=25.1). Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 7.5 pts (4.0 pts below line; 63% blended confidence [T3]). Risk: minutes trending down (21.6 L10 vs 25.1 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -12334,29 +12334,29 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.539</v>
+        <v>0.765</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>22.6</v>
+        <v>-0.5</v>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="J65" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="K65" t="n">
-        <v>1.333</v>
+        <v>1.465</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Barrett's L30 of 19.0 pts sits 2.5 below the 21.5 line — marginally supports the OVER. FG% +5.5% trending (L10 vs L30). Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 5/10 agree (HR L10, Trend, Defense); counter-signals: Volume, HR L30, Context. Projection model targets 22.6 pts (1.1 pts above line; 53% blended confidence [T3]). Risk: only 33% hit rate over L30 suggests the line may be set fairly.</t>
+          <t>Recent scoring trending up 2.9 pts (L5 vs L30) — marginally supports the UNDER. FG% +13.7% trending (L10 vs L30); Minutes up 2.0 recently (L10=23.9 vs L30=21.9). Opponent is weak defense (#25) at moderate pace (#15). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets -0.5 pts (11.0 pts below line; 76% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -12397,10 +12397,10 @@
         <v>0.4</v>
       </c>
       <c r="J66" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K66" t="n">
-        <v>1.385</v>
+        <v>1.408</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
@@ -12445,10 +12445,10 @@
         <v>3.1</v>
       </c>
       <c r="J67" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="K67" t="n">
-        <v>1.385</v>
+        <v>1.435</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
@@ -12541,10 +12541,10 @@
         <v>3.1</v>
       </c>
       <c r="J69" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="K69" t="n">
-        <v>1.465</v>
+        <v>1.408</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -12589,10 +12589,10 @@
         <v>4.5</v>
       </c>
       <c r="J70" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="K70" t="n">
-        <v>1.435</v>
+        <v>1.385</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
@@ -12637,10 +12637,10 @@
         <v>3.2</v>
       </c>
       <c r="J71" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="K71" t="n">
-        <v>1.476</v>
+        <v>1.5</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
@@ -12685,10 +12685,10 @@
         <v>4.8</v>
       </c>
       <c r="J72" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="K72" t="n">
-        <v>1.417</v>
+        <v>1.408</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
@@ -12733,10 +12733,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="K73" t="n">
-        <v>1.4</v>
+        <v>1.435</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
@@ -12766,29 +12766,29 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.554</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
-        <v>1.769</v>
+        <v>2.7</v>
       </c>
       <c r="K74" t="n">
-        <v>1.98</v>
+        <v>1.435</v>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Poeltl's L30 average of 10.5 pts vs the 10.5 line — marginally supports the UNDER. FG% -8.8% trending (L10 vs L30). Opponent is weak defense (#29) at moderate pace (#15). Mixed signals: 4/10 agree (HR L30, Trend, Context); counter-signals: Volume, HR L10, Defense. Projection model targets 8.9 pts (1.6 pts below line; 55% blended confidence [T3]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
+          <t>Poeltl's L30 average of 10.5 pts vs the 11.5 line — marginally supports the UNDER. FG% -8.8% trending (L10 vs L30). Opponent is weak defense (#29) at moderate pace (#15). Mixed signals: 5/10 agree (Volume, HR L30, Trend); counter-signals: HR L10, Defense, H2H. Projection model targets 8.8 pts (2.7 pts below line; 56% blended confidence [T3]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -12829,10 +12829,10 @@
         <v>5.6</v>
       </c>
       <c r="J75" t="n">
-        <v>1.847</v>
+        <v>1.877</v>
       </c>
       <c r="K75" t="n">
-        <v>1.909</v>
+        <v>1.877</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
@@ -12877,10 +12877,10 @@
         <v>0.4</v>
       </c>
       <c r="J76" t="n">
-        <v>1.813</v>
+        <v>1.82</v>
       </c>
       <c r="K76" t="n">
-        <v>1.952</v>
+        <v>1.943</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
@@ -12925,10 +12925,10 @@
         <v>1.3</v>
       </c>
       <c r="J77" t="n">
-        <v>1.8</v>
+        <v>1.926</v>
       </c>
       <c r="K77" t="n">
-        <v>1.971</v>
+        <v>1.833</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -12973,10 +12973,10 @@
         <v>4.9</v>
       </c>
       <c r="J78" t="n">
-        <v>1.847</v>
+        <v>1.862</v>
       </c>
       <c r="K78" t="n">
-        <v>1.909</v>
+        <v>1.901</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -13021,10 +13021,10 @@
         <v>4.8</v>
       </c>
       <c r="J79" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="K79" t="n">
-        <v>1.917</v>
+        <v>1.893</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.719</v>
       </c>
       <c r="F81" t="n">
         <v>4</v>
@@ -13114,17 +13114,17 @@
         <v>10.7</v>
       </c>
       <c r="I81" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J81" t="n">
         <v>1.813</v>
       </c>
       <c r="K81" t="n">
-        <v>1.962</v>
+        <v>1.952</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Sexton averages 12.8 pts in 4 meetings (-5.7 vs line) — marginally supports the UNDER. H2H avg 2.3 pts below season L30; TS% shifts -5.1% in this matchup. Opponent is below-average defense (#22) at above-average pace (#12). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 10.7 pts (7.8 pts below line; 68% blended confidence [T3]). Risk: L3 has surged to 22.7 after a 5-pt outing (7.6 above L30) — momentum could push over the under line.</t>
+          <t>Sexton averages 12.8 pts in 4 meetings (-6.7 vs line) — marginally supports the UNDER. H2H avg 2.3 pts below season L30; TS% shifts -5.1% in this matchup. Opponent is below-average defense (#22) at above-average pace (#12). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 10.7 pts (8.8 pts below line; 71% blended confidence [T3]). Risk: L3 has surged to 22.7 after a 5-pt outing (7.6 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -13165,10 +13165,10 @@
         <v>1.7</v>
       </c>
       <c r="J82" t="n">
-        <v>1.87</v>
+        <v>1.877</v>
       </c>
       <c r="K82" t="n">
-        <v>1.893</v>
+        <v>1.877</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
@@ -13213,10 +13213,10 @@
         <v>4.4</v>
       </c>
       <c r="J83" t="n">
-        <v>1.971</v>
+        <v>1.943</v>
       </c>
       <c r="K83" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
@@ -13261,10 +13261,10 @@
         <v>1.4</v>
       </c>
       <c r="J84" t="n">
-        <v>1.833</v>
+        <v>1.862</v>
       </c>
       <c r="K84" t="n">
-        <v>1.926</v>
+        <v>1.901</v>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
@@ -13309,10 +13309,10 @@
         <v>5.3</v>
       </c>
       <c r="J85" t="n">
-        <v>1.971</v>
+        <v>1.926</v>
       </c>
       <c r="K85" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
@@ -13357,10 +13357,10 @@
         <v>0.6</v>
       </c>
       <c r="J86" t="n">
-        <v>1.833</v>
+        <v>1.813</v>
       </c>
       <c r="K86" t="n">
-        <v>1.926</v>
+        <v>1.952</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
@@ -13405,10 +13405,10 @@
         <v>3.5</v>
       </c>
       <c r="J87" t="n">
-        <v>1.901</v>
+        <v>1.893</v>
       </c>
       <c r="K87" t="n">
-        <v>1.862</v>
+        <v>1.87</v>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
@@ -13453,10 +13453,10 @@
         <v>2.5</v>
       </c>
       <c r="J88" t="n">
-        <v>1.971</v>
+        <v>1.926</v>
       </c>
       <c r="K88" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
@@ -13501,10 +13501,10 @@
         <v>2.6</v>
       </c>
       <c r="J89" t="n">
-        <v>1.877</v>
+        <v>1.893</v>
       </c>
       <c r="K89" t="n">
-        <v>1.877</v>
+        <v>1.87</v>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         <v>1.3</v>
       </c>
       <c r="J90" t="n">
-        <v>1.98</v>
+        <v>1.813</v>
       </c>
       <c r="K90" t="n">
-        <v>1.787</v>
+        <v>1.952</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
@@ -13597,10 +13597,10 @@
         <v>2.5</v>
       </c>
       <c r="J91" t="n">
-        <v>1.943</v>
+        <v>1.917</v>
       </c>
       <c r="K91" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -13645,10 +13645,10 @@
         <v>3</v>
       </c>
       <c r="J92" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K92" t="n">
         <v>1.893</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1.87</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
@@ -13741,10 +13741,10 @@
         <v>0.6</v>
       </c>
       <c r="J94" t="n">
-        <v>1.84</v>
+        <v>1.943</v>
       </c>
       <c r="K94" t="n">
-        <v>1.917</v>
+        <v>1.82</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
@@ -13789,10 +13789,10 @@
         <v>1.2</v>
       </c>
       <c r="J95" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="K95" t="n">
-        <v>1.781</v>
+        <v>1.769</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
@@ -13837,10 +13837,10 @@
         <v>4.7</v>
       </c>
       <c r="J96" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>1.787</v>
+        <v>1.769</v>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
@@ -13885,10 +13885,10 @@
         <v>1.5</v>
       </c>
       <c r="J97" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="K97" t="n">
-        <v>1.917</v>
+        <v>1.943</v>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
@@ -13981,10 +13981,10 @@
         <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>1.84</v>
+        <v>1.833</v>
       </c>
       <c r="K99" t="n">
-        <v>1.917</v>
+        <v>1.926</v>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
@@ -14029,10 +14029,10 @@
         <v>1.9</v>
       </c>
       <c r="J100" t="n">
-        <v>1.926</v>
+        <v>1.99</v>
       </c>
       <c r="K100" t="n">
-        <v>1.833</v>
+        <v>1.781</v>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
@@ -14077,10 +14077,10 @@
         <v>1.9</v>
       </c>
       <c r="J101" t="n">
-        <v>1.877</v>
+        <v>1.847</v>
       </c>
       <c r="K101" t="n">
-        <v>1.877</v>
+        <v>1.909</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
@@ -14125,10 +14125,10 @@
         <v>3.1</v>
       </c>
       <c r="J102" t="n">
-        <v>1.893</v>
+        <v>1.877</v>
       </c>
       <c r="K102" t="n">
-        <v>1.87</v>
+        <v>1.877</v>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
@@ -14173,10 +14173,10 @@
         <v>4.8</v>
       </c>
       <c r="J103" t="n">
-        <v>1.901</v>
+        <v>1.893</v>
       </c>
       <c r="K103" t="n">
-        <v>1.862</v>
+        <v>1.87</v>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
@@ -14269,10 +14269,10 @@
         <v>0.3</v>
       </c>
       <c r="J105" t="n">
+        <v>1.862</v>
+      </c>
+      <c r="K105" t="n">
         <v>1.901</v>
-      </c>
-      <c r="K105" t="n">
-        <v>1.862</v>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
@@ -14413,10 +14413,10 @@
         <v>3.3</v>
       </c>
       <c r="J108" t="n">
-        <v>1.943</v>
+        <v>1.917</v>
       </c>
       <c r="K108" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="6">
@@ -14647,7 +14647,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="10">
@@ -14733,7 +14733,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -14747,7 +14747,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="15">
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="26">
@@ -15333,7 +15333,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -15343,17 +15343,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>25.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -15363,11 +15363,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="46">
@@ -15393,7 +15393,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Gary Trent Jr.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -15407,13 +15407,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gary Trent Jr.</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -15427,7 +15427,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="49">
@@ -15693,7 +15693,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -15703,17 +15703,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>18.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -15723,17 +15723,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -15747,13 +15747,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -15763,11 +15763,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>21.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="66">
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="75">
@@ -16087,7 +16087,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="82">

--- a/daily/2026-04-01.xlsx
+++ b/daily/2026-04-01.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1530,7 +1548,6 @@
       <c r="V13" t="n">
         <v>29</v>
       </c>
-      <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
         <v>-14.6</v>
       </c>
@@ -1936,7 +1953,6 @@
       <c r="V18" t="n">
         <v>23</v>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
         <v>40.2</v>
       </c>
@@ -2014,7 +2030,6 @@
       <c r="V19" t="n">
         <v>11</v>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
         <v>18.1</v>
       </c>
@@ -2092,7 +2107,6 @@
       <c r="V20" t="n">
         <v>11</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>24</v>
       </c>
@@ -2416,7 +2430,6 @@
       <c r="V24" t="n">
         <v>23</v>
       </c>
-      <c r="W24" t="inlineStr"/>
       <c r="X24" t="n">
         <v>5.7</v>
       </c>
@@ -2494,7 +2507,6 @@
       <c r="V25" t="n">
         <v>23</v>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
         <v>35.3</v>
       </c>
@@ -3720,7 +3732,6 @@
       <c r="V40" t="n">
         <v>14</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>9.1</v>
       </c>
@@ -3798,7 +3809,6 @@
       <c r="V41" t="n">
         <v>22</v>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
         <v>-48.6</v>
       </c>
@@ -3958,7 +3968,6 @@
       <c r="V43" t="n">
         <v>22</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>0</v>
       </c>
@@ -4036,7 +4045,6 @@
       <c r="V44" t="n">
         <v>22</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="n">
         <v>12.4</v>
       </c>
@@ -4196,7 +4204,6 @@
       <c r="V46" t="n">
         <v>14</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>13.1</v>
       </c>
@@ -4520,7 +4527,6 @@
       <c r="V50" t="n">
         <v>27</v>
       </c>
-      <c r="W50" t="inlineStr"/>
       <c r="X50" t="n">
         <v>-14.5</v>
       </c>
@@ -4598,7 +4604,6 @@
       <c r="V51" t="n">
         <v>27</v>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="n">
         <v>-13.5</v>
       </c>
@@ -4840,7 +4845,6 @@
       <c r="V54" t="n">
         <v>27</v>
       </c>
-      <c r="W54" t="inlineStr"/>
       <c r="X54" t="n">
         <v>2.8</v>
       </c>
@@ -5000,7 +5004,6 @@
       <c r="V56" t="n">
         <v>27</v>
       </c>
-      <c r="W56" t="inlineStr"/>
       <c r="X56" t="n">
         <v>12.7</v>
       </c>
@@ -5324,7 +5327,6 @@
       <c r="V60" t="n">
         <v>27</v>
       </c>
-      <c r="W60" t="inlineStr"/>
       <c r="X60" t="n">
         <v>0</v>
       </c>
@@ -5402,7 +5404,6 @@
       <c r="V61" t="n">
         <v>15</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="n">
         <v>-5</v>
       </c>
@@ -5562,7 +5563,6 @@
       <c r="V63" t="n">
         <v>15</v>
       </c>
-      <c r="W63" t="inlineStr"/>
       <c r="X63" t="n">
         <v>0</v>
       </c>
@@ -5640,7 +5640,6 @@
       <c r="V64" t="n">
         <v>15</v>
       </c>
-      <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
         <v>-32.6</v>
       </c>
@@ -5882,7 +5881,6 @@
       <c r="V67" t="n">
         <v>15</v>
       </c>
-      <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
         <v>-0.4</v>
       </c>
@@ -5960,7 +5958,6 @@
       <c r="V68" t="n">
         <v>25</v>
       </c>
-      <c r="W68" t="inlineStr"/>
       <c r="X68" t="n">
         <v>-6.6</v>
       </c>
@@ -6120,7 +6117,6 @@
       <c r="V70" t="n">
         <v>25</v>
       </c>
-      <c r="W70" t="inlineStr"/>
       <c r="X70" t="n">
         <v>0</v>
       </c>
@@ -6198,7 +6194,6 @@
       <c r="V71" t="n">
         <v>25</v>
       </c>
-      <c r="W71" t="inlineStr"/>
       <c r="X71" t="n">
         <v>-12</v>
       </c>
@@ -6358,7 +6353,6 @@
       <c r="V73" t="n">
         <v>15</v>
       </c>
-      <c r="W73" t="inlineStr"/>
       <c r="X73" t="n">
         <v>3.5</v>
       </c>
@@ -6436,7 +6430,6 @@
       <c r="V74" t="n">
         <v>25</v>
       </c>
-      <c r="W74" t="inlineStr"/>
       <c r="X74" t="n">
         <v>-9</v>
       </c>
@@ -6514,7 +6507,6 @@
       <c r="V75" t="n">
         <v>1</v>
       </c>
-      <c r="W75" t="inlineStr"/>
       <c r="X75" t="n">
         <v>0</v>
       </c>
@@ -6756,7 +6748,6 @@
       <c r="V78" t="n">
         <v>1</v>
       </c>
-      <c r="W78" t="inlineStr"/>
       <c r="X78" t="n">
         <v>-24.2</v>
       </c>
@@ -6834,7 +6825,6 @@
       <c r="V79" t="n">
         <v>12</v>
       </c>
-      <c r="W79" t="inlineStr"/>
       <c r="X79" t="n">
         <v>9.4</v>
       </c>
@@ -8388,7 +8378,6 @@
       <c r="V98" t="n">
         <v>9</v>
       </c>
-      <c r="W98" t="inlineStr"/>
       <c r="X98" t="n">
         <v>11.5</v>
       </c>
@@ -8466,7 +8455,6 @@
       <c r="V99" t="n">
         <v>9</v>
       </c>
-      <c r="W99" t="inlineStr"/>
       <c r="X99" t="n">
         <v>3.8</v>
       </c>
@@ -8544,7 +8532,6 @@
       <c r="V100" t="n">
         <v>13</v>
       </c>
-      <c r="W100" t="inlineStr"/>
       <c r="X100" t="n">
         <v>11.7</v>
       </c>
@@ -9015,7 +9002,7 @@
         <v>50</v>
       </c>
       <c r="Q106" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>5.7</v>
@@ -14747,2183 +14734,4945 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Banchero scored 11 pts vs 23.5 line (-12.5), OVER missed by 12.5 pts. Banchero played 26 min (-8.9 vs L10 avg of 35.2) — 25% less than expected. Shooting efficiency was cold: 33.3% FG (-8.5% vs L10 avg of 41.8%). 3/9 from the field. Counter-signals that proved correct: HR L30, HR L10, FG Trend, Min Trend. Signals that were wrong: Volume, Trend, Context. Projection model targeted 24.2 pts — actual 11 was 13.2 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Banchero for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 18 pts vs 22.5 line (-4.5), UNDER hit by 4.5 pts. Johnson played 34 min (-3.2 vs L10 avg of 36.7) — 9% less than expected. Shooting was in line with averages: 47.1% FG (8/17, L10 avg 49.1%). Signals that called it correctly: Volume, Context, Defense, H2H, Pace (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 18.8 pts — actual 18 was 0.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Johnson in this role.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bane scored 14 pts vs 19.5 line (-5.5), OVER missed by 5.5 pts. Bane played 30 min (-3.5 vs L10 avg of 33.3) — 11% less than expected. Shooting efficiency was cold: 38.5% FG (-7.0% vs L10 avg of 45.5%). 5/13 from the field. Counter-signals that proved correct: HR L10, Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 19.4 pts — actual 14 was 5.4 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E5" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Alexander-Walker scored 32 pts vs 19.5 line (+12.5), OVER hit by 12.5 pts. Minutes were as expected: 33 played vs L10 avg 33.1. Shooting efficiency was hot: 68.8% FG (+17.3% vs L10 avg of 51.5%). 11/16 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: H2H, Pace, Min Trend. Projection model targeted 24.0 pts — actual 32 was 8.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Alexander-Walker's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CJ McCollum</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>WIN — McCollum scored 9 pts vs 18.5 line (-9.5), UNDER hit by 9.5 pts. McCollum played 34 min (+4.4 vs L10 avg of 29.2) — 15% more than expected. Shooting efficiency was cold: 30.8% FG (-18.1% vs L10 avg of 48.9%). 4/13 from the field. Signals that called it correctly: Context, H2H, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.4 pts — actual 9 was 4.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms McCollum's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Suggs scored 7 pts vs 14.5 line (-7.5), UNDER hit by 7.5 pts. Suggs played 26 min (-5.5 vs L10 avg of 31.5) — 17% less than expected. Shooting efficiency was cold: 25.0% FG (-19.3% vs L10 avg of 44.3%). 3/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 8.6 pts — actual 7 was 1.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Suggs in this role.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Onyeka Okongwu</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Okongwu scored 16 pts vs 13.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 31 played vs L10 avg 29.1. Shooting efficiency was cold: 36.4% FG (-9.3% vs L10 avg of 45.7%). 4/11 from the field. Counter-signals that proved correct: Volume, HR L30, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 13.4 pts — actual 16 was 2.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Wagner scored 12 pts vs 12.5 line (-0.5), OVER missed by 0.5 pts. Wagner played 20 min (-6.5 vs L10 avg of 26.3) — 25% less than expected. Shooting efficiency was cold: 38.5% FG (-11.2% vs L10 avg of 49.7%). 5/13 from the field. Counter-signals that proved correct: Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.8 pts — actual 12 was 6.8 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Wagner for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Daniels scored 15 pts vs 11.5 line (+3.5), UNDER missed by 3.5 pts. Minutes were as expected: 31 played vs L10 avg 32.7. Shooting efficiency was cold: 45.5% FG (-10.6% vs L10 avg of 56.1%). 5/11 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Pace. Projection model targeted 11.0 pts — actual 15 was 4.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 14 pts vs 10.5 line (+3.5), UNDER missed by 3.5 pts. Jr. played 25 min (-5.1 vs L10 avg of 30.2) — 17% less than expected. Shooting efficiency was hot: 66.7% FG (+12.2% vs L10 avg of 54.5%). 6/9 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, H2H. Projection model targeted 9.8 pts — actual 14 was 4.2 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Jr. for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Silva scored 9 pts vs 9.5 line (-0.5), OVER missed by 0.5 pts. Silva played 23 min (-5.6 vs L10 avg of 28.6) — 20% less than expected. Shooting was in line with averages: 40.0% FG (2/5, L10 avg 43.7%). Counter-signals that proved correct: FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.3 pts — actual 9 was 4.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Silva for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Jonathan Kuminga</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Kuminga scored 12 pts vs 9.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 19 played vs L10 avg 21.4. Shooting efficiency was hot: 71.4% FG (+34.4% vs L10 avg of 37.0%). 5/7 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 4.4 pts — actual 12 was 7.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Jock Landale</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Landale scored 8 pts vs 6.5 line (+1.5), OVER hit by 1.5 pts. Landale played 15 min (-5.1 vs L10 avg of 19.7) — 26% less than expected. Shooting efficiency was hot: 75.0% FG (+26.7% vs L10 avg of 48.3%). 3/4 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 8.6 pts — actual 8 was 0.6 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Landale in this role.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Edgecombe scored 23 pts vs 15.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 33 played vs L10 avg 32.9. Shooting efficiency was hot: 66.7% FG (+19.0% vs L10 avg of 47.7%). 10/15 from the field. Counter-signals that proved correct: Volume, HR L10, Trend, Defense. Signals that were wrong: HR L30, Context, H2H. Projection model targeted 12.0 pts — actual 23 was 11.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 12 pts vs 12.5 line (-0.5), UNDER hit by 0.5 pts. Jr. played 21 min (-10.3 vs L10 avg of 31.1) — 33% less than expected. Shooting efficiency was hot: 50.0% FG (+5.0% vs L10 avg of 45.0%). 5/10 from the field. Signals that called it correctly: H2H, Min Trend (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.8 pts — actual 12 was 1.2 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jr. in this role.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Maxey scored 28 pts vs 28.5 line (-0.5), OVER missed by 0.5 pts. Maxey played 34 min (-3.4 vs L10 avg of 37.4) — 9% less than expected. Shooting efficiency was hot: 60.0% FG (+16.5% vs L10 avg of 43.5%). 12/20 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, Pace. Projection model targeted 30.4 pts — actual 28 was 2.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Will Riley</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E18" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Riley scored 18 pts vs 14.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 32 played vs L10 avg 31.5. Shooting efficiency was hot: 66.7% FG (+21.7% vs L10 avg of 45.0%). 8/12 from the field. Signals that called it correctly: Volume, HR L10, Trend, Context, Defense (6/10 aligned). Counter-signals that were wrong: HR L30, H2H, Pace. Projection model targeted 15.6 pts — actual 18 was 2.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Riley's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — George scored 39 pts vs 19.5 line (+19.5), UNDER missed by 19.5 pts. Minutes were as expected: 30 played vs L10 avg 32.5. Shooting efficiency was hot: 68.2% FG (+23.4% vs L10 avg of 44.8%). 15/22 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.8 pts — actual 39 was 22.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Barlow scored 6 pts vs 6.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 22 played vs L10 avg 22.5. Shooting efficiency was hot: 100.0% FG (+45.1% vs L10 avg of 54.9%). 3/3 from the field. Counter-signals that proved correct: Trend, H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.8 pts — actual 6 was 3.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Adem Bona</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bona scored 13 pts vs 7.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 21 played vs L10 avg 18.5. Shooting efficiency was hot: 100.0% FG (+48.2% vs L10 avg of 51.8%). 5/5 from the field. Counter-signals that proved correct: Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 3.9 pts — actual 13 was 9.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Quentin Grimes</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Grimes scored 12 pts vs 13.5 line (-1.5), OVER missed by 1.5 pts. Grimes played 23 min (-9.5 vs L10 avg of 32.6) — 29% less than expected. Shooting was in line with averages: 50.0% FG (5/10, L10 avg 46.0%). Counter-signals that proved correct: Volume, HR L30, FG Trend. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 16.9 pts — actual 12 was 4.9 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Grimes for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Bilal Coulibaly</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E23" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Coulibaly scored 12 pts vs 12.5 line (-0.5), UNDER hit by 0.5 pts. Coulibaly played 19 min (-8.6 vs L10 avg of 27.8) — 31% less than expected. Shooting efficiency was hot: 50.0% FG (+10.6% vs L10 avg of 39.4%). 5/10 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, Pace (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 8.3 pts — actual 12 was 3.7 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Coulibaly's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Tre Johnson</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Johnson scored 8 pts vs 12.5 line (-4.5), OVER missed by 4.5 pts. Minutes were as expected: 24 played vs L10 avg 22.8. Shooting efficiency was cold: 27.3% FG (-10.9% vs L10 avg of 38.2%). 3/11 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, H2H. Signals that were wrong: Volume, Context, Defense. Projection model targeted 13.3 pts — actual 8 was 5.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Anthony Gill</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Gill scored 21 pts vs 7.5 line (+13.5), OVER hit by 13.5 pts. Gill played 34 min (+10.1 vs L10 avg of 24.4) — 41% more than expected. Shooting efficiency was hot: 88.9% FG (+38.1% vs L10 avg of 50.8%). 8/9 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Defense (6/10 aligned). Counter-signals that were wrong: Volume, H2H, Pace. Projection model targeted 8.8 pts — actual 21 was 12.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Gill's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Tristan Vukcevic</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E26" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Vukcevic scored 17 pts vs 12.5 line (+4.5), OVER hit by 4.5 pts. Vukcevic played 11 min (-5.8 vs L10 avg of 17.1) — 34% less than expected. Shooting efficiency was hot: 85.7% FG (+38.6% vs L10 avg of 47.1%). 6/7 from the field. Signals that called it correctly: Trend, Defense, H2H, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.9 pts — actual 17 was 4.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Vukcevic's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Jayson Tatum</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Tatum scored 25 pts vs 23.5 line (+1.5), UNDER missed by 1.5 pts. Tatum played 37 min (+5.8 vs L10 avg of 31.4) — 18% more than expected. Shooting was in line with averages: 42.9% FG (9/21, L10 avg 39.7%). Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 22.2 pts — actual 25 was 2.8 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E28" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Wiggins scored 13 pts vs 14.5 line (-1.5), UNDER hit by 1.5 pts. Wiggins played 32 min (+3.9 vs L10 avg of 28.2) — 14% more than expected. Shooting efficiency was hot: 57.1% FG (+8.9% vs L10 avg of 48.2%). 4/7 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Defense (8/10 aligned). Counter-signals that were wrong: Volume, H2H. Projection model targeted 12.5 pts — actual 13 was 0.5 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Davion Mitchell</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E29" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 21 pts vs 8.5 line (+12.5), OVER hit by 12.5 pts. Mitchell played 40 min (+11.3 vs L10 avg of 29.1) — 39% more than expected. Shooting efficiency was hot: 53.3% FG (+5.2% vs L10 avg of 48.1%). 8/15 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 10.2 pts — actual 21 was 10.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Mitchell's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Baylor Scheierman</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E30" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Scheierman scored 8 pts vs 5.5 line (+2.5), UNDER missed by 2.5 pts. Scheierman played 18 min (-8.6 vs L10 avg of 26.4) — 33% less than expected. Shooting efficiency was hot: 75.0% FG (+32.8% vs L10 avg of 42.2%). 3/4 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, H2H. Projection model targeted 2.6 pts — actual 8 was 5.4 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Scheierman for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Tyler Herro</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Herro scored 18 pts vs 22.5 line (-4.5), UNDER hit by 4.5 pts. Herro played 40 min (+7.3 vs L10 avg of 33.0) — 22% more than expected. Shooting efficiency was cold: 33.3% FG (-12.3% vs L10 avg of 45.6%). 5/15 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, Min Trend. Projection model targeted 18.3 pts — actual 18 was 0.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Neemias Queta</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E32" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Queta scored 16 pts vs 9.5 line (+6.5), UNDER missed by 6.5 pts. Queta played 33 min (+6.2 vs L10 avg of 26.9) — 23% more than expected. Shooting efficiency was hot: 71.4% FG (+9.1% vs L10 avg of 62.3%). 5/7 from the field. Counter-signals that proved correct: Volume, Trend, Pace, FG Trend. Signals that were wrong: HR L30, HR L10, Context. Projection model targeted 7.7 pts — actual 16 was 8.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Payton Pritchard</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Pritchard scored 14 pts vs 15.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 31 played vs L10 avg 32.6. Shooting efficiency was hot: 55.6% FG (+13.1% vs L10 avg of 42.5%). 5/9 from the field. Signals that called it correctly: H2H, FG Trend (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.3 pts — actual 14 was 0.3 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Pritchard in this role.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Adebayo scored 29 pts vs 21.5 line (+7.5), OVER hit by 7.5 pts. Minutes were as expected: 38 played vs L10 avg 36.6. Shooting efficiency was hot: 47.6% FG (+9.0% vs L10 avg of 38.6%). 10/21 from the field. Signals that called it correctly: Volume, Context, Min Trend (3/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 22.7 pts — actual 29 was 6.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Adebayo's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Derrick White</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>WIN — White scored 6 pts vs 16.5 line (-10.5), UNDER hit by 10.5 pts. Minutes were as expected: 34 played vs L10 avg 34.6. Shooting efficiency was hot: 75.0% FG (+39.5% vs L10 avg of 35.5%). 3/4 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 15.7 pts — actual 6 was 9.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms White's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Sam Hauser</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hauser scored 23 pts vs 7.5 line (+15.5), OVER hit by 15.5 pts. Hauser played 29 min (+3.8 vs L10 avg of 24.9) — 15% more than expected. Shooting efficiency was hot: 81.8% FG (+48.0% vs L10 avg of 33.8%). 9/11 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 8.2 pts — actual 23 was 14.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Hauser's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Jaylen Brown</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Brown scored 43 pts vs 26.5 line (+16.5), OVER hit by 16.5 pts. Minutes were as expected: 37 played vs L10 avg 35.1. Shooting efficiency was hot: 58.6% FG (+14.2% vs L10 avg of 44.4%). 17/29 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: FG Trend. Projection model targeted 27.8 pts — actual 43 was 15.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Pelle Larsson</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Larsson scored 18 pts vs 12.5 line (+5.5), UNDER missed by 5.5 pts. Larsson played 38 min (+5.9 vs L10 avg of 32.0) — 18% more than expected. Shooting was in line with averages: 53.8% FG (7/13, L10 avg 52.9%). Counter-signals that proved correct: Volume, HR L30, HR L10, FG Trend. Signals that were wrong: Trend, Context, Defense. Projection model targeted 11.2 pts — actual 18 was 6.8 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Larsson's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E39" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 17 pts vs 13.5 line (+3.5), UNDER missed by 3.5 pts. Jr. played 30 min (+4.2 vs L10 avg of 25.6) — 16% more than expected. Shooting was in line with averages: 43.8% FG (7/16, L10 avg 45.1%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 11.5 pts — actual 17 was 5.5 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Jr.'s recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E40" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Sheppard scored 27 pts vs 14.5 line (+12.5), UNDER missed by 12.5 pts. Sheppard played 37 min (+7.8 vs L10 avg of 29.3) — 27% more than expected. Shooting efficiency was hot: 60.0% FG (+16.9% vs L10 avg of 43.1%). 9/15 from the field. Counter-signals that proved correct: Volume, Defense, H2H, Pace. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 9.9 pts — actual 27 was 17.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Ousmane Dieng</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Dieng scored 36 pts vs 13.5 line (+22.5), UNDER missed by 22.5 pts. Dieng played 45 min (+16.2 vs L10 avg of 28.5) — 57% more than expected. Shooting efficiency was hot: 48.4% FG (+5.4% vs L10 avg of 43.0%). 15/31 from the field. Counter-signals that proved correct: Trend, H2H, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 1.4 pts — actual 36 was 34.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Amen Thompson</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E42" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Thompson scored 18 pts vs 15.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 40 played vs L10 avg 39.2. Shooting was in line with averages: 50.0% FG (5/10, L10 avg 54.5%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, H2H. Projection model targeted 12.2 pts — actual 18 was 5.8 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Thompson's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Jericho Sims</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Sims scored 6 pts vs 6.5 line (-0.5), UNDER hit by 0.5 pts. Sims played 36 min (+13.7 vs L10 avg of 22.0) — 62% more than expected. Shooting efficiency was cold: 20.0% FG (-58.1% vs L10 avg of 78.1%). 1/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (9/10 aligned). Counter-signals that were wrong: Trend. Projection model targeted 3.4 pts — actual 6 was 2.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Ryan Rollins</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="5" t="n">
         <v>19.5</v>
       </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Jabari Smith Jr.</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E45" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 12 pts vs 14.5 line (-2.5), UNDER hit by 2.5 pts. Jr. played 33 min (-5.1 vs L10 avg of 38.2) — 13% less than expected. Shooting efficiency was cold: 33.3% FG (-9.2% vs L10 avg of 42.5%). 5/15 from the field. Signals that called it correctly: Trend, H2H, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.5 pts — actual 12 was 0.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jr. in this role.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Kevin Durant</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E46" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Durant scored 19 pts vs 23.5 line (-4.5), OVER missed by 4.5 pts. Durant played 39 min (+3.0 vs L10 avg of 36.3) — 8% more than expected. Shooting efficiency was cold: 43.8% FG (-10.5% vs L10 avg of 54.3%). 7/16 from the field. Counter-signals that proved correct: H2H. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 27.9 pts — actual 19 was 8.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Gary Trent Jr.</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 0 pts vs 17.5 line (-17.5), UNDER hit by 17.5 pts. Jr. played 8 min (-14.6 vs L10 avg of 22.1) — 66% less than expected. Shooting efficiency was cold: 0.0% FG (-37.9% vs L10 avg of 37.9%). 0/3 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (7/10 aligned). Counter-signals that were wrong: Trend, FG Trend, Min Trend. Projection model targeted 9.0 pts — actual 0 was 9.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Alperen Sengun</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E48" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Sengun scored 25 pts vs 18.5 line (+6.5), OVER hit by 6.5 pts. Sengun played 30 min (-3.5 vs L10 avg of 33.0) — 11% less than expected. Shooting efficiency was hot: 69.2% FG (+7.3% vs L10 avg of 61.9%). 9/13 from the field. Signals that called it correctly: Volume, Trend, Context, H2H, Pace (7/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Defense. Projection model targeted 21.6 pts — actual 25 was 3.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Sengun's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Tari Eason</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Eason scored 5 pts vs 9.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 24 played vs L10 avg 24.6. Shooting efficiency was cold: 12.5% FG (-19.1% vs L10 avg of 31.6%). 1/8 from the field. Signals that called it correctly: HR L30, Context, H2H, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 7.6 pts — actual 5 was 2.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Eason's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E50" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Coward scored 15 pts vs 13.5 line (+1.5), UNDER missed by 1.5 pts. Coward played 28 min (+4.2 vs L10 avg of 24.1) — 17% more than expected. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 43.7%). Counter-signals that proved correct: HR L10, Trend, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 9.1 pts — actual 15 was 5.9 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E51" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jackson scored 20 pts vs 16.5 line (+3.5), UNDER missed by 3.5 pts. Minutes were as expected: 25 played vs L10 avg 26.0. Shooting efficiency was hot: 66.7% FG (+18.2% vs L10 avg of 48.5%). 8/12 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 11.5 pts — actual 20 was 8.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E52" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Bridges scored 24 pts vs 14.5 line (+9.5), OVER hit by 9.5 pts. Bridges played 36 min (+4.5 vs L10 avg of 31.4) — 14% more than expected. Shooting efficiency was hot: 60.0% FG (+15.1% vs L10 avg of 44.9%). 9/15 from the field. Signals that called it correctly: Defense, H2H, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.0 pts — actual 24 was 8.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bridges's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E53" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hart scored 5 pts vs 12.5 line (-7.5), UNDER hit by 7.5 pts. Hart played 25 min (-6.0 vs L10 avg of 30.9) — 19% less than expected. Shooting efficiency was cold: 50.0% FG (-8.4% vs L10 avg of 58.4%). 2/4 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.2 pts — actual 5 was 1.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Hart in this role.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Cam Spencer</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E54" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Spencer scored 10 pts vs 9.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 22 played vs L10 avg 24.2. Shooting efficiency was hot: 50.0% FG (+8.9% vs L10 avg of 41.1%). 2/4 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Min Trend (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 10.3 pts — actual 10 was 0.3 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Spencer in this role.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Towns scored 20 pts vs 21.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 30 played vs L10 avg 29.8. Shooting efficiency was hot: 66.7% FG (+10.8% vs L10 avg of 55.9%). 8/12 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 15.6 pts — actual 20 was 4.4 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Towns's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Walter Clayton Jr.</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 10 pts vs 7.5 line (+2.5), OVER hit by 2.5 pts. Jr. played 23 min (-3.0 vs L10 avg of 25.6) — 12% less than expected. Shooting efficiency was hot: 42.9% FG (+9.4% vs L10 avg of 33.5%). 3/7 from the field. Signals that called it correctly: Volume, HR L10, Trend, Context, FG Trend (6/10 aligned). Counter-signals that were wrong: HR L30, Defense, H2H. Projection model targeted 12.9 pts — actual 10 was 2.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Anunoby scored 25 pts vs 17.5 line (+7.5), UNDER missed by 7.5 pts. Anunoby played 40 min (+6.0 vs L10 avg of 33.7) — 18% more than expected. Shooting was in line with averages: 47.1% FG (8/17, L10 avg 50.3%). Counter-signals that proved correct: Defense, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 15.9 pts — actual 25 was 9.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Jalen Brunson</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="5" t="n">
         <v>22.5</v>
       </c>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Jordan Clarkson</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E59" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Clarkson scored 8 pts vs 10.5 line (-2.5), OVER missed by 2.5 pts. Clarkson played 11 min (-9.9 vs L10 avg of 21.1) — 47% less than expected. Shooting efficiency was hot: 75.0% FG (+23.3% vs L10 avg of 51.7%). 3/4 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, Pace. Projection model targeted 11.1 pts — actual 8 was 3.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Clarkson for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E60" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Prosper scored 17 pts vs 10.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 24 played vs L10 avg 24.8. Shooting was in line with averages: 54.5% FG (6/11, L10 avg 52.4%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 13.0 pts — actual 17 was 4.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Prosper's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>RJ Barrett</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E61" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Barrett scored 20 pts vs 22.5 line (-2.5), UNDER hit by 2.5 pts. Barrett played 36 min (+6.0 vs L10 avg of 30.3) — 20% more than expected. Shooting efficiency was cold: 42.1% FG (-12.4% vs L10 avg of 54.5%). 8/19 from the field. Signals that called it correctly: Volume, HR L30, Context (3/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 22.6 pts — actual 20 was 2.6 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Barrett's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>DeMar DeRozan</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E62" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>WIN — DeRozan scored 28 pts vs 18.5 line (+9.5), OVER hit by 9.5 pts. DeRozan played 35 min (+4.0 vs L10 avg of 30.9) — 13% more than expected. Shooting efficiency was cold: 38.9% FG (-10.8% vs L10 avg of 49.7%). 7/18 from the field. Signals that called it correctly: Context, H2H, FG Trend, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.7 pts — actual 28 was 7.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms DeRozan's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Collin Murray-Boyles</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E63" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Murray-Boyles scored 20 pts vs 11.5 line (+8.5), UNDER missed by 8.5 pts. Murray-Boyles played 18 min (-3.6 vs L10 avg of 21.6) — 17% less than expected. Shooting efficiency was hot: 77.8% FG (+6.4% vs L10 avg of 71.4%). 7/9 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.5 pts — actual 20 was 12.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Ja'Kobe Walter</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E64" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Walter scored 8 pts vs 10.5 line (-2.5), UNDER hit by 2.5 pts. Walter played 32 min (+8.4 vs L10 avg of 23.9) — 35% more than expected. Shooting efficiency was hot: 75.0% FG (+19.9% vs L10 avg of 55.1%). 3/4 from the field. Signals that called it correctly: Volume, HR L30, Context (3/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted -0.5 pts — actual 8 was 8.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Walter's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Malik Monk</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E65" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Monk scored 18 pts vs 15.5 line (+2.5), UNDER missed by 2.5 pts. Monk played 29 min (+5.0 vs L10 avg of 24.2) — 21% more than expected. Shooting efficiency was hot: 54.5% FG (+12.9% vs L10 avg of 41.6%). 6/11 from the field. Counter-signals that proved correct: H2H, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.5 pts — actual 18 was 4.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Precious Achiuwa</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E66" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Achiuwa scored 28 pts vs 11.5 line (+16.5), OVER hit by 16.5 pts. Achiuwa played 38 min (+8.0 vs L10 avg of 30.0) — 27% more than expected. Shooting efficiency was hot: 63.2% FG (+6.9% vs L10 avg of 56.3%). 12/19 from the field. Signals that called it correctly: Volume, HR L10, Trend, Context, FG Trend (6/10 aligned). Counter-signals that were wrong: HR L30, Defense, H2H. Projection model targeted 15.3 pts — actual 28 was 12.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Achiuwa's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Jakob Poeltl</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E67" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Poeltl scored 18 pts vs 10.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 28 played vs L10 avg 26.0. Shooting efficiency was hot: 75.0% FG (+14.1% vs L10 avg of 60.9%). 6/8 from the field. Counter-signals that proved correct: Volume, HR L10, Defense, H2H. Signals that were wrong: HR L30, Trend, Context. Projection model targeted 8.9 pts — actual 18 was 9.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Maxime Raynaud</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E68" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Raynaud scored 6 pts vs 14.5 line (-8.5), UNDER hit by 8.5 pts. Raynaud played 23 min (-9.8 vs L10 avg of 32.9) — 30% less than expected. Shooting efficiency was cold: 50.0% FG (-5.8% vs L10 avg of 55.8%). 2/4 from the field. Signals that called it correctly: HR L30, Context, Defense, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 11.4 pts — actual 6 was 5.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Raynaud's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Jamal Shead</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E69" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Shead scored 16 pts vs 8.5 line (+7.5), UNDER missed by 7.5 pts. Shead played 37 min (+12.4 vs L10 avg of 24.7) — 50% more than expected. Shooting efficiency was hot: 55.6% FG (+27.1% vs L10 avg of 28.5%). 5/9 from the field. Counter-signals that proved correct: Trend, Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.4 pts — actual 16 was 10.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Devin Carter</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E70" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Carter scored 13 pts vs 12.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 23 played vs L10 avg 21.7. Shooting efficiency was cold: 33.3% FG (-6.6% vs L10 avg of 39.9%). 4/12 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 8.0 pts — actual 13 was 5.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Nique Clifford</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E71" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Clifford scored 9 pts vs 10.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 32 played vs L10 avg 31.6. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 40.9%). Signals that called it correctly: HR L30, Trend, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: Volume, HR L10, H2H. Projection model targeted 5.7 pts — actual 9 was 3.3 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Clifford's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Sandro Mamukelashvili</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E72" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Mamukelashvili scored 17 pts vs 13.5 line (+3.5), UNDER missed by 3.5 pts. Mamukelashvili played 33 min (+13.4 vs L10 avg of 19.7) — 68% more than expected. Shooting efficiency was hot: 70.0% FG (+10.8% vs L10 avg of 59.2%). 7/10 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 13.5 pts — actual 17 was 3.5 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E73" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Barnes scored 14 pts vs 20.5 line (-6.5), UNDER hit by 6.5 pts. Barnes played 35 min (+4.5 vs L10 avg of 30.8) — 15% more than expected. Shooting efficiency was cold: 35.7% FG (-20.3% vs L10 avg of 56.0%). 5/14 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 18.9 pts — actual 14 was 4.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Barnes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Dylan Cardwell</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="4" t="n">
         <v>4.5</v>
       </c>
+      <c r="E74" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Cardwell scored 2 pts vs 4.5 line (-2.5), UNDER hit by 2.5 pts. Cardwell played 14 min (-3.9 vs L10 avg of 18.3) — 21% less than expected. Shooting efficiency was cold: 33.3% FG (-18.6% vs L10 avg of 51.9%). 1/3 from the field. Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 2.3 pts — actual 2 was 0.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Cardwell in this role.</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Kam Jones</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E75" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jones scored 9 pts vs 8.5 line (+0.5), UNDER missed by 0.5 pts. Jones played 25 min (+5.6 vs L10 avg of 19.7) — 28% more than expected. Shooting efficiency was hot: 50.0% FG (+11.7% vs L10 avg of 38.3%). 4/8 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 2.9 pts — actual 9 was 6.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E76" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Siakam scored 25 pts vs 26.5 line (-1.5), UNDER hit by 1.5 pts. Siakam played 22 min (-9.8 vs L10 avg of 31.4) — 31% less than expected. Shooting efficiency was hot: 68.8% FG (+22.0% vs L10 avg of 46.8%). 11/16 from the field. Signals that called it correctly: Volume, HR L30, Trend, Context, H2H (7/10 aligned). Counter-signals that were wrong: HR L10, Defense, Pace. Projection model targeted 25.7 pts — actual 25 was 0.7 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Siakam in this role.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Jay Huff</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E77" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Huff scored 17 pts vs 11.5 line (+5.5), OVER hit by 5.5 pts. Huff played 17 min (-3.9 vs L10 avg of 20.7) — 19% less than expected. Shooting efficiency was hot: 75.0% FG (+25.7% vs L10 avg of 49.3%). 6/8 from the field. Signals that called it correctly: Defense, H2H, Pace, FG Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.9 pts — actual 17 was 3.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Huff's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Quenton Jackson</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E78" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jackson scored 8 pts vs 13.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 17 played vs L10 avg 16.2. Shooting efficiency was hot: 50.0% FG (+7.3% vs L10 avg of 42.7%). 3/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 2.6 pts — actual 8 was 5.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jackson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Nick Richards</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="5" t="n">
         <v>10.5</v>
       </c>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="5" t="inlineStr"/>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>Tre Jones</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E80" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 15 pts vs 16.5 line (-1.5), UNDER hit by 1.5 pts. Jones played 25 min (-3.1 vs L10 avg of 28.3) — 11% less than expected. Shooting efficiency was hot: 63.6% FG (+6.1% vs L10 avg of 57.5%). 7/11 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 16.1 pts — actual 15 was 1.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jones in this role.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>Josh Giddey</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="5" t="n">
         <v>18.5</v>
       </c>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="5" t="inlineStr"/>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>Isaac Okoro</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E82" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Okoro scored 14 pts vs 10.5 line (+3.5), UNDER missed by 3.5 pts. Okoro played 26 min (-3.5 vs L10 avg of 29.7) — 12% less than expected. Shooting efficiency was hot: 80.0% FG (+41.3% vs L10 avg of 38.7%). 4/5 from the field. Counter-signals that proved correct: Trend, Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.7 pts — actual 14 was 8.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Collin Sexton</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E83" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Sexton scored 18 pts vs 19.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 26 played vs L10 avg 25.8. Shooting efficiency was hot: 57.1% FG (+5.9% vs L10 avg of 51.2%). 8/14 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 10.7 pts — actual 18 was 7.3 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Sexton's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>Matas Buzelis</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E84" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Buzelis scored 17 pts vs 21.5 line (-4.5), UNDER hit by 4.5 pts. Buzelis played 29 min (-4.2 vs L10 avg of 33.1) — 13% less than expected. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 42.9%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 19.8 pts — actual 17 was 2.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Buzelis's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Nikola Jokić</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E85" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jokić scored 15 pts vs 24.5 line (-9.5), UNDER hit by 9.5 pts. Jokić played 33 min (-3.5 vs L10 avg of 36.6) — 10% less than expected. Shooting efficiency was cold: 50.0% FG (-7.0% vs L10 avg of 57.0%). 5/10 from the field. Signals that called it correctly: HR L10, Trend (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 23.1 pts — actual 15 was 8.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jokić's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>Jamal Murray</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E86" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Murray scored 37 pts vs 24.5 line (+12.5), OVER hit by 12.5 pts. Minutes were as expected: 37 played vs L10 avg 36.7. Shooting was in line with averages: 46.2% FG (12/26, L10 avg 46.9%). Signals that called it correctly: Volume, Trend, Context, Defense, H2H (8/10 aligned). Counter-signals that were wrong: HR L30, HR L10. Projection model targeted 29.8 pts — actual 37 was 7.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>Cameron Johnson</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E87" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 19 pts vs 11.5 line (+7.5), OVER hit by 7.5 pts. Johnson played 36 min (+5.8 vs L10 avg of 29.7) — 20% more than expected. Shooting was in line with averages: 53.8% FG (7/13, L10 avg 53.2%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: Min Trend. Projection model targeted 12.1 pts — actual 19 was 6.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>Aaron Gordon</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E88" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Gordon scored 6 pts vs 15.5 line (-9.5), UNDER hit by 9.5 pts. Minutes were as expected: 28 played vs L10 avg 25.5. Shooting efficiency was cold: 14.3% FG (-28.8% vs L10 avg of 43.1%). 1/7 from the field. Signals that called it correctly: Trend, Context, H2H, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.0 pts — actual 6 was 6.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Gordon's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>Cody Williams</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E89" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Williams scored 9 pts vs 15.5 line (-6.5), UNDER hit by 6.5 pts. Williams played 38 min (+4.4 vs L10 avg of 33.2) — 13% more than expected. Shooting efficiency was cold: 30.0% FG (-19.6% vs L10 avg of 49.6%). 3/10 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 13.0 pts — actual 9 was 4.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Williams's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>Ace Bailey</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E90" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Bailey scored 12 pts vs 20.5 line (-8.5), UNDER hit by 8.5 pts. Bailey played 34 min (+4.0 vs L10 avg of 29.5) — 14% more than expected. Shooting efficiency was cold: 29.4% FG (-21.1% vs L10 avg of 50.5%). 5/17 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 16.9 pts — actual 12 was 4.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bailey's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Tim Hardaway Jr.</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E91" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 3 pts vs 12.5 line (-9.5), OVER missed by 9.5 pts. Jr. played 10 min (-14.4 vs L10 avg of 24.8) — 58% less than expected. Shooting efficiency was hot: 50.0% FG (+15.6% vs L10 avg of 34.4%). 1/2 from the field. Counter-signals that proved correct: HR L10, Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 13.8 pts — actual 3 was 10.8 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Jr. for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Bruce Brown</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E92" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Brown scored 11 pts vs 7.5 line (+3.5), OVER hit by 3.5 pts. Brown played 27 min (+6.6 vs L10 avg of 20.6) — 32% more than expected. Shooting was in line with averages: 50.0% FG (4/8, L10 avg 51.5%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: Min Trend. Projection model targeted 10.0 pts — actual 11 was 1.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Peyton Watson</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E93" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Watson scored 6 pts vs 12.5 line (-6.5), OVER missed by 6.5 pts. Watson played 9 min (-20.7 vs L10 avg of 30.1) — 69% less than expected. Shooting efficiency was hot: 60.0% FG (+17.5% vs L10 avg of 42.5%). 3/5 from the field. Counter-signals that proved correct: Trend, H2H, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 15.5 pts — actual 6 was 9.5 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Watson for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Brice Sensabaugh</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="3" t="n">
         <v>22.5</v>
       </c>
+      <c r="E94" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Sensabaugh scored 28 pts vs 22.5 line (+5.5), UNDER missed by 5.5 pts. Sensabaugh played 33 min (+4.4 vs L10 avg of 28.3) — 16% more than expected. Shooting efficiency was hot: 61.1% FG (+8.9% vs L10 avg of 52.2%). 11/18 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 15.6 pts — actual 28 was 12.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>Kyle Filipowski</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E95" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Filipowski scored 25 pts vs 15.5 line (+9.5), OVER hit by 9.5 pts. Filipowski played 31 min (+5.4 vs L10 avg of 25.2) — 21% more than expected. Shooting efficiency was hot: 60.0% FG (+10.8% vs L10 avg of 49.2%). 9/15 from the field. Signals that called it correctly: Trend, Pace, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.1 pts — actual 25 was 8.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Filipowski's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>Christian Braun</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E96" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Braun scored 18 pts vs 11.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 31 played vs L10 avg 31.3. Shooting efficiency was hot: 63.6% FG (+8.0% vs L10 avg of 55.6%). 7/11 from the field. Signals that called it correctly: HR L10, Trend, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, Min Trend. Projection model targeted 12.7 pts — actual 18 was 5.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Braun's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>John Konchar</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E97" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Konchar scored 12 pts vs 6.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 29 played vs L10 avg 27.7. Shooting efficiency was hot: 57.1% FG (+13.3% vs L10 avg of 43.8%). 4/7 from the field. Signals that called it correctly: Trend, Pace, FG Trend, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.8 pts — actual 12 was 5.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Konchar's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Will Richard</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E98" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Richard scored 2 pts vs 9.5 line (-7.5), UNDER hit by 7.5 pts. Minutes were as expected: 26 played vs L10 avg 26.2. Shooting efficiency was cold: 33.3% FG (-19.4% vs L10 avg of 52.7%). 1/3 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (5/10 aligned). Counter-signals that were wrong: Trend, H2H, Pace. Projection model targeted 4.8 pts — actual 2 was 2.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Richard's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>Pat Spencer</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E99" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Spencer scored 14 pts vs 10.5 line (+3.5), OVER hit by 3.5 pts. Spencer played 38 min (+17.1 vs L10 avg of 20.9) — 82% more than expected. Shooting efficiency was cold: 40.0% FG (-5.2% vs L10 avg of 45.2%). 6/15 from the field. Signals that called it correctly: Trend, Pace, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.2 pts — actual 14 was 2.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Spencer's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E100" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Harper scored 13 pts vs 12.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 24 played vs L10 avg 24.2. Shooting was in line with averages: 54.5% FG (6/11, L10 avg 57.6%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: H2H. Projection model targeted 14.4 pts — actual 13 was 1.4 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>De'Aaron Fox</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E101" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Fox scored 11 pts vs 16.5 line (-5.5), UNDER hit by 5.5 pts. Fox played 25 min (-4.2 vs L10 avg of 28.9) — 15% less than expected. Shooting efficiency was hot: 57.1% FG (+7.5% vs L10 avg of 49.6%). 4/7 from the field. Signals that called it correctly: HR L30, Trend, Context, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L10, Defense. Projection model targeted 14.6 pts — actual 11 was 3.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Fox's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>Brandin Podziemski</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E102" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Podziemski scored 14 pts vs 16.5 line (-2.5), UNDER hit by 2.5 pts. Podziemski played 17 min (-15.1 vs L10 avg of 32.3) — 47% less than expected. Shooting efficiency was hot: 50.0% FG (+7.5% vs L10 avg of 42.5%). 4/8 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Pace. Projection model targeted 14.2 pts — actual 14 was 0.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Podziemski in this role.</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Stephon Castle</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E103" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Castle scored 15 pts vs 16.5 line (-1.5), OVER missed by 1.5 pts. Castle played 33 min (+3.3 vs L10 avg of 29.4) — 11% more than expected. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 49.3%). Counter-signals that proved correct: Volume, HR L30, Trend, H2H. Signals that were wrong: HR L10, Context, Defense. Projection model targeted 16.5 pts — actual 15 was 1.5 pts close (wrong direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>Devin Vassell</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E104" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Vassell scored 8 pts vs 12.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 28 played vs L10 avg 29.8. Shooting efficiency was cold: 25.0% FG (-15.9% vs L10 avg of 40.9%). 2/8 from the field. Signals that called it correctly: HR L30, Trend, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L10, Defense. Projection model targeted 8.3 pts — actual 8 was 0.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Vassell in this role.</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>Victor Wembanyama</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E105" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Wembanyama scored 41 pts vs 25.5 line (+15.5), OVER hit by 15.5 pts. Minutes were as expected: 29 played vs L10 avg 29.9. Shooting efficiency was hot: 72.7% FG (+22.9% vs L10 avg of 49.8%). 16/22 from the field. Signals that called it correctly: Trend, H2H, Pace, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 27.3 pts — actual 41 was 13.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Wembanyama's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>Keldon Johnson</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E106" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Johnson scored 11 pts vs 12.5 line (-1.5), OVER missed by 1.5 pts. Johnson played 26 min (+3.1 vs L10 avg of 22.6) — 14% more than expected. Shooting efficiency was cold: 27.3% FG (-24.5% vs L10 avg of 51.8%). 3/11 from the field. Counter-signals that proved correct: Volume, HR L30, Defense. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 14.5 pts — actual 11 was 3.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>Gui Santos</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="5" t="n">
         <v>16.5</v>
       </c>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="5" t="inlineStr"/>
+      <c r="I107" s="5" t="n"/>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>Julian Champagnie</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E108" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Champagnie scored 15 pts vs 9.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 26 played vs L10 avg 26.9. Shooting efficiency was cold: 33.3% FG (-13.5% vs L10 avg of 46.8%). 5/15 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Pace. Signals that were wrong: Trend, Context, Defense. Projection model targeted 7.9 pts — actual 15 was 7.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t>Draymond Green</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E109" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Green scored 14 pts vs 8.5 line (+5.5), OVER hit by 5.5 pts. Green played 21 min (-9.6 vs L10 avg of 30.3) — 32% less than expected. Shooting efficiency was hot: 57.1% FG (+15.5% vs L10 avg of 41.6%). 4/7 from the field. Signals that called it correctly: Trend, Context, H2H, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.2 pts — actual 14 was 4.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Green's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>Gary Payton II</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="5" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="5" t="n">
         <v>12.5</v>
+      </c>
+      <c r="E110" s="5" t="n"/>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="5" t="inlineStr"/>
+      <c r="I110" s="5" t="n"/>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
       </c>
     </row>
   </sheetData>
